--- a/docs/eval/eval_report_extended.xlsx
+++ b/docs/eval/eval_report_extended.xlsx
@@ -602,7 +602,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-30 07:50:49 UTC</t>
+          <t>Generated 2026-10-31 14:59:58 UTC</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>17 / 31 ms</t>
+          <t>25 / 43 ms</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>19.4</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>22.9</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>25.9</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>21.5</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>24.3</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>34.5</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>42.4</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-30T07:50:48+00:00</t>
+          <t>2026-10-31T14:59:57+00:00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-30 07:50:49 UTC</t>
+          <t>2026-10-31 14:59:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-30T07:50:48+00:00</t>
+          <t>2026-10-31T14:59:57+00:00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-30T07:50:48+00:00</t>
+          <t>2026-10-31T14:59:57+00:00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-30T07:50:48+00:00</t>
+          <t>2026-10-31T14:59:57+00:00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-30T07:50:48+00:00</t>
+          <t>2026-10-31T14:59:57+00:00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-30T07:50:48+00:00</t>
+          <t>2026-10-31T14:59:57+00:00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-30T07:50:48+00:00</t>
+          <t>2026-10-31T14:59:57+00:00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
